--- a/Assessment Questions/AIE/ADS-114/Gen AI and Agentic AI Essentials/Generative Adversarial Networks (GANs) core concepts/Generative Adversarial Networks (GANs) core concepts.xlsx
+++ b/Assessment Questions/AIE/ADS-114/Gen AI and Agentic AI Essentials/Generative Adversarial Networks (GANs) core concepts/Generative Adversarial Networks (GANs) core concepts.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GANs Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,12 +444,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
